--- a/workshop_registration_form_templates/028_data_driven_processing_summit_registration--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/028_data_driven_processing_summit_registration--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_accept_the_terms_and_conditions',_'value':_true}</t>
+          <t>i_accept_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I accept the terms and conditions', 'value': True}</t>
+          <t>I accept the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_accept_the_terms_and_conditions',_'value':_false}</t>
+          <t>i_do_not_accept_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'I do not accept the terms and conditions', 'value': False}</t>
+          <t>I do not accept the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'virtual',_'value':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Virtual', 'value': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'in-person',_'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'In-person', 'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Both', 'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian',_'value':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian', 'value': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'vegan',_'value':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan', 'value': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'gluten-free',_'value':_'gluten-free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Gluten-free', 'value': 'Gluten-free'}</t>
+          <t>Gluten-free</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above',_'value':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above', 'value': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'online_payment',_'value':_'online_payment'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Online payment', 'value': 'Online payment'}</t>
+          <t>Online payment</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'offline_payment',_'value':_'offline_payment'}</t>
+          <t>offline_payment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Offline payment', 'value': 'Offline payment'}</t>
+          <t>Offline payment</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_any_food_allergies',_'value':_'i_have_any_food_allergies'}</t>
+          <t>i_have_any_food_allergies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'I have any food allergies', 'value': 'I have any food allergies'}</t>
+          <t>I have any food allergies</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_any_medical_conditions',_'value':_'i_have_any_medical_conditions'}</t>
+          <t>i_have_any_medical_conditions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'I have any medical conditions', 'value': 'I have any medical conditions'}</t>
+          <t>I have any medical conditions</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above',_'value':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above', 'value': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
